--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA56"/>
+  <dimension ref="A1:BA54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -671,13 +671,13 @@
         <v>0.2980849292256453</v>
       </c>
       <c r="J2" t="n">
-        <v>368</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>489</v>
+        <v>24</v>
       </c>
       <c r="L2" t="n">
-        <v>347</v>
+        <v>14</v>
       </c>
       <c r="M2" t="n">
         <v>413</v>
@@ -752,13 +752,13 @@
         <v>1.051428571428571</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.02330508474576271</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.065359477124183</v>
+        <v>0.05228758169934641</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.644549763033175</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AN2" t="n">
         <v>1.736730360934183</v>
@@ -801,13 +801,13 @@
         <v>0.2980849292256453</v>
       </c>
       <c r="J3" t="n">
-        <v>9.684210526315789</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="K3" t="n">
-        <v>12.86842105263158</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="L3" t="n">
-        <v>9.131578947368421</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="M3" t="n">
         <v>10.86842105263158</v>
@@ -882,13 +882,13 @@
         <v>1.051428571428572</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7796610169491526</v>
+        <v>0.02330508474576271</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.065359477124183</v>
+        <v>0.0522875816993464</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.644549763033176</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="AN3" t="n">
         <v>1.736730360934183</v>
@@ -931,13 +931,13 @@
         <v>0.1866452131938858</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>453</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>327</v>
+        <v>15</v>
       </c>
       <c r="M4" t="n">
         <v>418</v>
@@ -1012,13 +1012,13 @@
         <v>1.083180987202925</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7919320594479831</v>
+        <v>0.02123142250530785</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.083732057416268</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.857954545454545</v>
+        <v>2.5</v>
       </c>
       <c r="AN4" t="n">
         <v>1.542372881355932</v>
@@ -1061,13 +1061,13 @@
         <v>0.1866452131938858</v>
       </c>
       <c r="J5" t="n">
-        <v>9.815789473684211</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="K5" t="n">
-        <v>11.92105263157895</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="L5" t="n">
-        <v>8.605263157894736</v>
+        <v>0.3947368421052632</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
@@ -1142,13 +1142,13 @@
         <v>1.083180987202925</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.791932059447983</v>
+        <v>0.02123142250530785</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.083732057416268</v>
+        <v>0.02631578947368421</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.857954545454545</v>
+        <v>2.5</v>
       </c>
       <c r="AN5" t="n">
         <v>1.542372881355932</v>
@@ -1486,16 +1486,16 @@
         <v>304</v>
       </c>
       <c r="U8" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="W8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>34</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>1444:54</t>
+          <t>768:21</t>
         </is>
       </c>
       <c r="AO8" t="n">
@@ -1575,13 +1575,13 @@
         <v>6.918</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.068</v>
+        <v>0.127</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.02</v>
+        <v>0.037</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.048</v>
+        <v>0.089</v>
       </c>
       <c r="BA8" t="n">
         <v>0.169</v>
@@ -1651,10 +1651,10 @@
         <v>82</v>
       </c>
       <c r="U9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>780:55</t>
+          <t>380:17</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,13 +1740,13 @@
         <v>4.586</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.079</v>
+        <v>0.161</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.015</v>
+        <v>0.032</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.022</v>
+        <v>0.044</v>
       </c>
       <c r="BA9" t="n">
         <v>0.034</v>
@@ -1981,16 +1981,16 @@
         <v>281</v>
       </c>
       <c r="U11" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>102</v>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>1230:48</t>
+          <t>634:28</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2070,13 +2070,13 @@
         <v>7.588</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.093</v>
+        <v>0.181</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.021</v>
+        <v>0.042</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.067</v>
+        <v>0.13</v>
       </c>
       <c r="BA11" t="n">
         <v>0.07199999999999999</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>60:59</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,13 +2235,13 @@
         <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.061</v>
+        <v>0.179</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.018</v>
+        <v>0.054</v>
       </c>
       <c r="BA12" t="n">
         <v>0.005</v>
@@ -2311,16 +2311,16 @@
         <v>25</v>
       </c>
       <c r="U13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>304:45</t>
+          <t>125:28</t>
         </is>
       </c>
       <c r="AO13" t="n">
@@ -2400,13 +2400,13 @@
         <v>3.143</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.073</v>
+        <v>0.178</v>
       </c>
       <c r="AY13" t="n">
         <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.015</v>
+        <v>0.036</v>
       </c>
       <c r="BA13" t="n">
         <v>0.013</v>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AO14" t="n">
@@ -2568,10 +2568,10 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.051</v>
+        <v>0.089</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.096</v>
+        <v>0.168</v>
       </c>
       <c r="BA14" t="n">
         <v>0.004</v>
@@ -2641,16 +2641,16 @@
         <v>14</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
         <v>8</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>192:59</t>
+          <t>92:12</t>
         </is>
       </c>
       <c r="AO15" t="n">
@@ -2730,13 +2730,13 @@
         <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.064</v>
+        <v>0.133</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.012</v>
+        <v>0.026</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.047</v>
+        <v>0.098</v>
       </c>
       <c r="BA15" t="n">
         <v>0.008999999999999999</v>
@@ -2806,16 +2806,16 @@
         <v>809</v>
       </c>
       <c r="U16" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>97</v>
+        <v>6</v>
       </c>
       <c r="W16" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="X16" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
         <v>262</v>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2007:19</t>
+          <t>965:33</t>
         </is>
       </c>
       <c r="AO16" t="n">
@@ -2895,13 +2895,13 @@
         <v>12.105</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.123</v>
+        <v>0.256</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.032</v>
+        <v>0.066</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.097</v>
+        <v>0.202</v>
       </c>
       <c r="BA16" t="n">
         <v>0.044</v>
@@ -2971,16 +2971,16 @@
         <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
         <v>9</v>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>957:27</t>
+          <t>438:14</t>
         </is>
       </c>
       <c r="AO17" t="n">
@@ -3060,13 +3060,13 @@
         <v>4.581</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.062</v>
+        <v>0.134</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.053</v>
+        <v>0.116</v>
       </c>
       <c r="BA17" t="n">
         <v>0.044</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>1</v>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>34:32</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AO18" t="n">
@@ -3225,10 +3225,10 @@
         <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.068</v>
+        <v>0.161</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.165</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -3301,16 +3301,16 @@
         <v>619</v>
       </c>
       <c r="U19" t="n">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="n">
         <v>145</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2031:26</t>
+          <t>990:50</t>
         </is>
       </c>
       <c r="AO19" t="n">
@@ -3390,13 +3390,13 @@
         <v>7.474</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.139</v>
+        <v>0.285</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.04</v>
+        <v>0.082</v>
       </c>
       <c r="BA19" t="n">
         <v>0.111</v>
@@ -3466,16 +3466,16 @@
         <v>296</v>
       </c>
       <c r="U20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
         <v>78</v>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>978:05</t>
+          <t>557:17</t>
         </is>
       </c>
       <c r="AO20" t="n">
@@ -3555,13 +3555,13 @@
         <v>6.548</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.108</v>
+        <v>0.19</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.026</v>
+        <v>0.045</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.149</v>
       </c>
       <c r="BA20" t="n">
         <v>0.032</v>
@@ -3631,16 +3631,16 @@
         <v>726</v>
       </c>
       <c r="U21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
         <v>211</v>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1480:59</t>
+          <t>764:21</t>
         </is>
       </c>
       <c r="AO21" t="n">
@@ -3720,13 +3720,13 @@
         <v>8.962</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.169</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.171</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.107</v>
+        <v>0.208</v>
       </c>
       <c r="BA21" t="n">
         <v>0.046</v>
@@ -3796,16 +3796,16 @@
         <v>66</v>
       </c>
       <c r="U22" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
         <v>20</v>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>363:28</t>
+          <t>163:56</t>
         </is>
       </c>
       <c r="AO22" t="n">
@@ -3885,13 +3885,13 @@
         <v>5.5</v>
       </c>
       <c r="AX22" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>0.082</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0.037</v>
       </c>
       <c r="BA22" t="n">
         <v>0.02</v>
@@ -3967,10 +3967,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
         <v>3</v>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>32:28</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="AO23" t="n">
@@ -4050,13 +4050,13 @@
         <v>8</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="AY23" t="n">
-        <v>0.111</v>
+        <v>0.159</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.104</v>
+        <v>0.149</v>
       </c>
       <c r="BA23" t="n">
         <v>0.003</v>
@@ -4126,16 +4126,16 @@
         <v>411</v>
       </c>
       <c r="U24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
         <v>134</v>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>1049:14</t>
+          <t>513:16</t>
         </is>
       </c>
       <c r="AO24" t="n">
@@ -4215,13 +4215,13 @@
         <v>7.944</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.075</v>
+        <v>0.154</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.067</v>
+        <v>0.138</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.102</v>
+        <v>0.208</v>
       </c>
       <c r="BA24" t="n">
         <v>0.02</v>
@@ -4291,16 +4291,16 @@
         <v>107</v>
       </c>
       <c r="U25" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
         <v>41</v>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>519:43</t>
+          <t>254:21</t>
         </is>
       </c>
       <c r="AO25" t="n">
@@ -4380,13 +4380,13 @@
         <v>10.889</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.082</v>
+        <v>0.168</v>
       </c>
       <c r="AY25" t="n">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.041</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA25" t="n">
         <v>0.029</v>
@@ -4456,16 +4456,16 @@
         <v>152</v>
       </c>
       <c r="U26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
         <v>57</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>392:33</t>
+          <t>198:12</t>
         </is>
       </c>
       <c r="AO26" t="n">
@@ -4545,13 +4545,13 @@
         <v>4.923</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.092</v>
+        <v>0.182</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.073</v>
+        <v>0.145</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.077</v>
+        <v>0.153</v>
       </c>
       <c r="BA26" t="n">
         <v>0.016</v>
@@ -4621,16 +4621,16 @@
         <v>285</v>
       </c>
       <c r="U27" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="W27" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
         <v>81</v>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>1445:53</t>
+          <t>729:38</t>
         </is>
       </c>
       <c r="AO27" t="n">
@@ -4710,13 +4710,13 @@
         <v>7.339</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.13</v>
+        <v>0.258</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.012</v>
+        <v>0.025</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.033</v>
+        <v>0.066</v>
       </c>
       <c r="BA27" t="n">
         <v>0.089</v>
@@ -4890,163 +4890,163 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>38</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>3430</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>805</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>1352</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>910</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>471</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>859</v>
       </c>
       <c r="T29" t="n">
-        <v>118</v>
+        <v>4389</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1227</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>529</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>929</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>7650:00</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>28</v>
+        <v>3273.4</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>0.612</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.048</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.737</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>6.837</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="BA29" t="n">
         <v>0</v>
@@ -5055,44 +5055,44 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>38</v>
       </c>
       <c r="C30" t="n">
-        <v>3430</v>
+        <v>3183</v>
       </c>
       <c r="D30" t="n">
-        <v>805</v>
+        <v>767</v>
       </c>
       <c r="E30" t="n">
-        <v>1352</v>
+        <v>1392</v>
       </c>
       <c r="F30" t="n">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="G30" t="n">
-        <v>1050</v>
+        <v>1094</v>
       </c>
       <c r="H30" t="n">
-        <v>716</v>
+        <v>464</v>
       </c>
       <c r="I30" t="n">
-        <v>910</v>
+        <v>603</v>
       </c>
       <c r="J30" t="n">
-        <v>818</v>
+        <v>728</v>
       </c>
       <c r="K30" t="n">
-        <v>941</v>
+        <v>816</v>
       </c>
       <c r="L30" t="n">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>274</v>
       </c>
       <c r="N30" t="n">
         <v>165</v>
@@ -5101,76 +5101,76 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q30" t="n">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="R30" t="n">
-        <v>630</v>
+        <v>782</v>
       </c>
       <c r="S30" t="n">
-        <v>859</v>
+        <v>697</v>
       </c>
       <c r="T30" t="n">
-        <v>4389</v>
+        <v>3564</v>
       </c>
       <c r="U30" t="n">
-        <v>368</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>489</v>
+        <v>11</v>
       </c>
       <c r="W30" t="n">
-        <v>347</v>
+        <v>15</v>
       </c>
       <c r="X30" t="n">
-        <v>211</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>1227</v>
+        <v>952</v>
       </c>
       <c r="Z30" t="n">
-        <v>1435</v>
+        <v>1187</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.855</v>
+        <v>0.802</v>
       </c>
       <c r="AB30" t="n">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AC30" t="n">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.452</v>
+        <v>0.429</v>
       </c>
       <c r="AE30" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="AF30" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.529</v>
+        <v>0.361</v>
       </c>
       <c r="AH30" t="n">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="AI30" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.331</v>
+        <v>0.437</v>
       </c>
       <c r="AK30" t="n">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AL30" t="n">
-        <v>929</v>
+        <v>952</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5178,40 +5178,40 @@
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>3273.4</v>
+        <v>3223.32</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.547</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.612</v>
+        <v>0.578</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.048</v>
+        <v>0.987</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.144</v>
+        <v>0.146</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.298</v>
+        <v>0.187</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.737</v>
+        <v>1.542</v>
       </c>
       <c r="AV30" t="n">
-        <v>5.1</v>
+        <v>5.267</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.837</v>
+        <v>6.809</v>
       </c>
       <c r="AX30" t="n">
         <v>0.2</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.138</v>
+        <v>0.128</v>
       </c>
       <c r="BA30" t="n">
         <v>0</v>
@@ -5220,460 +5220,460 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>38</v>
-      </c>
-      <c r="C31" t="n">
-        <v>3183</v>
-      </c>
-      <c r="D31" t="n">
-        <v>767</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1392</v>
-      </c>
-      <c r="F31" t="n">
-        <v>395</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1094</v>
-      </c>
-      <c r="H31" t="n">
-        <v>464</v>
-      </c>
-      <c r="I31" t="n">
-        <v>603</v>
-      </c>
-      <c r="J31" t="n">
-        <v>728</v>
-      </c>
-      <c r="K31" t="n">
-        <v>816</v>
-      </c>
-      <c r="L31" t="n">
-        <v>418</v>
-      </c>
-      <c r="M31" t="n">
-        <v>274</v>
-      </c>
-      <c r="N31" t="n">
-        <v>165</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>472</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>418</v>
-      </c>
-      <c r="R31" t="n">
-        <v>782</v>
-      </c>
-      <c r="S31" t="n">
-        <v>697</v>
-      </c>
-      <c r="T31" t="n">
-        <v>3564</v>
-      </c>
-      <c r="U31" t="n">
-        <v>373</v>
-      </c>
-      <c r="V31" t="n">
-        <v>453</v>
-      </c>
-      <c r="W31" t="n">
-        <v>327</v>
-      </c>
-      <c r="X31" t="n">
-        <v>176</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>952</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1187</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>236</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>550</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>43</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>119</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>62</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>142</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>333</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>952</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>7650:00</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>3223.32</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.542</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>6.809</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0.128</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
-      <c r="BA32" t="inlineStr"/>
+          <t>#0 T. WALKUP (Per Game)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>32</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4.906</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.156</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.562</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J32" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.906</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.062</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="T32" t="n">
+        <v>304</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.094</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
+        <v>6.525</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.752</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.837</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>3.082</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>6.918</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0.202</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#0 T. WALKUP (Per Game)</t>
+          <t>#1 F. NTILIKINA (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C33" t="n">
-        <v>4.906</v>
+        <v>4.739</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0.783</v>
       </c>
       <c r="E33" t="n">
-        <v>2.156</v>
+        <v>1.957</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="G33" t="n">
-        <v>2.562</v>
+        <v>2.13</v>
       </c>
       <c r="H33" t="n">
-        <v>0.469</v>
+        <v>0.696</v>
       </c>
       <c r="I33" t="n">
-        <v>0.625</v>
+        <v>0.826</v>
       </c>
       <c r="J33" t="n">
-        <v>5.875</v>
+        <v>1.696</v>
       </c>
       <c r="K33" t="n">
-        <v>1.906</v>
+        <v>0.652</v>
       </c>
       <c r="L33" t="n">
-        <v>0.75</v>
+        <v>0.435</v>
       </c>
       <c r="M33" t="n">
-        <v>0.906</v>
+        <v>0.478</v>
       </c>
       <c r="N33" t="n">
-        <v>0.156</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.531</v>
+        <v>1.261</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.5</v>
+        <v>1.217</v>
       </c>
       <c r="R33" t="n">
-        <v>2.062</v>
+        <v>2.609</v>
       </c>
       <c r="S33" t="n">
-        <v>1.656</v>
+        <v>1.478</v>
       </c>
       <c r="T33" t="n">
-        <v>304</v>
+        <v>82</v>
       </c>
       <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.478</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0.913</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.5</v>
       </c>
-      <c r="V33" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.406</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.756</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.094</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.343</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.25</v>
-      </c>
       <c r="AH33" t="n">
-        <v>0.094</v>
+        <v>0.043</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.281</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.719</v>
+        <v>0.783</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.281</v>
+        <v>2.043</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.315</v>
+        <v>0.383</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>45:09</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.525</v>
+        <v>5.711</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.47</v>
+        <v>0.495</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.491</v>
+        <v>0.532</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.752</v>
+        <v>0.83</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.235</v>
+        <v>0.221</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.099</v>
+        <v>0.17</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.837</v>
+        <v>1.345</v>
       </c>
       <c r="AV33" t="n">
-        <v>3.082</v>
+        <v>3.241</v>
       </c>
       <c r="AW33" t="n">
-        <v>6.918</v>
+        <v>4.586</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.068</v>
+        <v>0.161</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.02</v>
+        <v>0.032</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.048</v>
+        <v>0.044</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.202</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#1 F. NTILIKINA (Per Game)</t>
+          <t>#2 K. EVANS (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>4.739</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.783</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>1.957</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>0.696</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>1.696</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.652</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.478</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.261</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.217</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.609</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.478</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>0.478</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.609</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5682,487 +5682,487 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.478</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.765</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.913</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.238</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.783</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.043</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.383</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>33:57</t>
+          <t>02:01</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>5.711</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.495</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.345</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.241</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.586</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.079</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#2 K. EVANS (Per Game)</t>
+          <t>#3 T. WARD (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7.125</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.656</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.344</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.469</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.969</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.281</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="T35" t="n">
+        <v>281</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>3.188</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.094</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AC35" t="n">
         <v>1</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>0.406</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>0.031</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>0.156</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>0.417</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>02:01</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>7.687</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>0.489</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>0.538</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>0.927</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>0.296</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2.324</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>5.265</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>7.588</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#3 T. WARD (Per Game)</t>
+          <t>#5 G. LARENTZAKIS (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C36" t="n">
-        <v>7.125</v>
+        <v>0.143</v>
       </c>
       <c r="D36" t="n">
-        <v>1.938</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>3.469</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>0.531</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.125</v>
+        <v>0.357</v>
       </c>
       <c r="H36" t="n">
-        <v>1.656</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>2.344</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>2.469</v>
+        <v>0.429</v>
       </c>
       <c r="K36" t="n">
-        <v>2.281</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6879999999999999</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0.594</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0.406</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.062</v>
+        <v>0.143</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.969</v>
+        <v>0.143</v>
       </c>
       <c r="R36" t="n">
-        <v>2.281</v>
+        <v>0.286</v>
       </c>
       <c r="S36" t="n">
-        <v>2.375</v>
+        <v>0.143</v>
       </c>
       <c r="T36" t="n">
-        <v>281</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.344</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0.844</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.188</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Z36" t="n">
-        <v>4.094</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.406</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.406</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0.156</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0.417</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.75</v>
+        <v>0.357</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>38:27</t>
+          <t>01:29</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>7.687</v>
+        <v>0.571</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.489</v>
+        <v>0.167</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.538</v>
+        <v>0.167</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.927</v>
+        <v>0.25</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.138</v>
+        <v>0.25</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.296</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.324</v>
+        <v>3</v>
       </c>
       <c r="AV36" t="n">
-        <v>5.265</v>
+        <v>3</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.588</v>
+        <v>6</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.093</v>
+        <v>0.179</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0.067</v>
+        <v>0.054</v>
       </c>
       <c r="BA36" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#5 G. LARENTZAKIS (Per Game)</t>
+          <t>#9 S. LEE (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C37" t="n">
-        <v>0.143</v>
+        <v>2.176</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.471</v>
       </c>
       <c r="E37" t="n">
-        <v>0.07099999999999999</v>
+        <v>1.059</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="G37" t="n">
-        <v>0.357</v>
+        <v>0.647</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>0.647</v>
       </c>
       <c r="J37" t="n">
-        <v>0.429</v>
+        <v>0.882</v>
       </c>
       <c r="K37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.235</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.143</v>
+        <v>0.824</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.143</v>
+        <v>0.647</v>
       </c>
       <c r="R37" t="n">
-        <v>0.286</v>
+        <v>0.706</v>
       </c>
       <c r="S37" t="n">
-        <v>0.143</v>
+        <v>0.412</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -6177,28 +6177,28 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.824</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>0.875</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>0.588</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -6213,157 +6213,157 @@
         <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.357</v>
+        <v>0.647</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>04:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>0.571</v>
+        <v>2.814</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.167</v>
+        <v>0.483</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.167</v>
+        <v>0.547</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.25</v>
+        <v>0.773</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.25</v>
+        <v>0.293</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="AU37" t="n">
-        <v>3</v>
+        <v>1.071</v>
       </c>
       <c r="AV37" t="n">
-        <v>3</v>
+        <v>2.071</v>
       </c>
       <c r="AW37" t="n">
-        <v>6</v>
+        <v>3.143</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.061</v>
+        <v>0.178</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.018</v>
+        <v>0.036</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.014</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#9 S. LEE (Per Game)</t>
+          <t>#10 M. FALL (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>2.176</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.471</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>1.059</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.529</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.882</v>
+        <v>1.667</v>
       </c>
       <c r="K38" t="n">
-        <v>0.235</v>
+        <v>0.667</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="M38" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0.176</v>
+        <v>0.667</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.412</v>
+        <v>0.333</v>
       </c>
       <c r="T38" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="U38" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.118</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.9409999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.176</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.588</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.059</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -6378,166 +6378,166 @@
         <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.647</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>04:28</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>2.814</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.483</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.547</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.293</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.071</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.071</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.143</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.015</v>
+        <v>0.168</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.029</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#10 M. FALL (Per Game)</t>
+          <t>#11 M. MORRIS (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
-        <v>1.667</v>
+        <v>1.1</v>
       </c>
       <c r="K39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>14</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.667</v>
       </c>
-      <c r="L39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="T39" t="n">
-        <v>11</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
       <c r="AH39" t="n">
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
@@ -6546,381 +6546,381 @@
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>07:49</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>2.628</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>0.292</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>0.495</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.051</v>
+        <v>0.026</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.096</v>
+        <v>0.098</v>
       </c>
       <c r="BA39" t="n">
-        <v>0.054</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#11 M. MORRIS (Per Game)</t>
+          <t>#14 S. VEZENKOV (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C40" t="n">
-        <v>1.3</v>
+        <v>19.441</v>
       </c>
       <c r="D40" t="n">
-        <v>0.3</v>
+        <v>4.941</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>7.912</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>1.735</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7</v>
+        <v>4.382</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7</v>
+        <v>4.353</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2</v>
+        <v>4.882</v>
       </c>
       <c r="J40" t="n">
-        <v>1.1</v>
+        <v>1.235</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8</v>
+        <v>5.088</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2</v>
+        <v>1.559</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1</v>
+        <v>0.618</v>
       </c>
       <c r="N40" t="n">
-        <v>0.3</v>
+        <v>0.324</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0.4</v>
+        <v>1.118</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.4</v>
+        <v>1.088</v>
       </c>
       <c r="R40" t="n">
-        <v>0.8</v>
+        <v>0.529</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7</v>
+        <v>3.324</v>
       </c>
       <c r="T40" t="n">
-        <v>14</v>
+        <v>809</v>
       </c>
       <c r="U40" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="W40" t="n">
-        <v>0.2</v>
+        <v>0.147</v>
       </c>
       <c r="X40" t="n">
-        <v>0.2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.8</v>
+        <v>7.706</v>
       </c>
       <c r="Z40" t="n">
-        <v>1</v>
+        <v>8.853</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.4</v>
+        <v>3.147</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>0.477</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.2</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.3</v>
+        <v>0.265</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.324</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.1</v>
+        <v>0.647</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.412</v>
       </c>
       <c r="AL40" t="n">
-        <v>0.6</v>
+        <v>3.735</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>0.378</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>28:23</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>2.628</v>
+        <v>15.56</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.176</v>
+        <v>0.614</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.292</v>
+        <v>0.673</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.495</v>
+        <v>1.249</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.152</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.412</v>
+        <v>0.354</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.75</v>
+        <v>1.105</v>
       </c>
       <c r="AV40" t="n">
-        <v>4.25</v>
+        <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>7</v>
+        <v>12.105</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.064</v>
+        <v>0.256</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.012</v>
+        <v>0.066</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.047</v>
+        <v>0.202</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.036</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#14 S. VEZENKOV (Per Game)</t>
+          <t>#16 K. PAPANIKOLAOU (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C41" t="n">
-        <v>19.441</v>
+        <v>2.788</v>
       </c>
       <c r="D41" t="n">
-        <v>4.941</v>
+        <v>0.273</v>
       </c>
       <c r="E41" t="n">
-        <v>7.912</v>
+        <v>0.424</v>
       </c>
       <c r="F41" t="n">
-        <v>1.735</v>
+        <v>0.727</v>
       </c>
       <c r="G41" t="n">
-        <v>4.382</v>
+        <v>2.364</v>
       </c>
       <c r="H41" t="n">
-        <v>4.353</v>
+        <v>0.061</v>
       </c>
       <c r="I41" t="n">
-        <v>4.882</v>
+        <v>0.212</v>
       </c>
       <c r="J41" t="n">
-        <v>1.235</v>
+        <v>1.515</v>
       </c>
       <c r="K41" t="n">
-        <v>5.088</v>
+        <v>1.364</v>
       </c>
       <c r="L41" t="n">
-        <v>1.559</v>
+        <v>0.242</v>
       </c>
       <c r="M41" t="n">
-        <v>0.618</v>
+        <v>0.333</v>
       </c>
       <c r="N41" t="n">
-        <v>0.324</v>
+        <v>0.152</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.118</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.088</v>
+        <v>0.848</v>
       </c>
       <c r="R41" t="n">
-        <v>0.529</v>
+        <v>1.485</v>
       </c>
       <c r="S41" t="n">
-        <v>3.324</v>
+        <v>0.333</v>
       </c>
       <c r="T41" t="n">
-        <v>809</v>
+        <v>78</v>
       </c>
       <c r="U41" t="n">
-        <v>2.412</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>2.853</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.265</v>
+        <v>0.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.412</v>
+        <v>0.03</v>
       </c>
       <c r="Y41" t="n">
-        <v>7.706</v>
+        <v>0.273</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.853</v>
+        <v>0.394</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.87</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.5</v>
+        <v>0.03</v>
       </c>
       <c r="AC41" t="n">
-        <v>3.147</v>
+        <v>0.061</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.477</v>
+        <v>0.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.03</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.265</v>
+        <v>0.03</v>
       </c>
       <c r="AG41" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.324</v>
+        <v>0.091</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.647</v>
+        <v>0.485</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.5</v>
+        <v>0.188</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.412</v>
+        <v>0.636</v>
       </c>
       <c r="AL41" t="n">
-        <v>3.735</v>
+        <v>1.879</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.378</v>
+        <v>0.339</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>59:02</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>15.56</v>
+        <v>3.821</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.614</v>
+        <v>0.489</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.673</v>
+        <v>0.484</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.249</v>
+        <v>0.73</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.246</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.354</v>
+        <v>0.022</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.105</v>
+        <v>1.613</v>
       </c>
       <c r="AV41" t="n">
-        <v>11</v>
+        <v>2.968</v>
       </c>
       <c r="AW41" t="n">
-        <v>12.105</v>
+        <v>4.581</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.123</v>
+        <v>0.134</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.032</v>
+        <v>0.022</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0.097</v>
+        <v>0.116</v>
       </c>
       <c r="BA41" t="n">
         <v>0.051</v>
@@ -6929,1085 +6929,1085 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#16 K. PAPANIKOLAOU (Per Game)</t>
+          <t>#21 O. NETZIPOGLOU (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C42" t="n">
-        <v>2.788</v>
+        <v>0.182</v>
       </c>
       <c r="D42" t="n">
-        <v>0.273</v>
+        <v>0.091</v>
       </c>
       <c r="E42" t="n">
-        <v>0.424</v>
+        <v>0.364</v>
       </c>
       <c r="F42" t="n">
-        <v>0.727</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.364</v>
+        <v>0.091</v>
       </c>
       <c r="H42" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1.515</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1.364</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.242</v>
+        <v>0.182</v>
       </c>
       <c r="M42" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0.9389999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.848</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.485</v>
+        <v>0.364</v>
       </c>
       <c r="S42" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>78</v>
+        <v>-4</v>
       </c>
       <c r="U42" t="n">
-        <v>0.212</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0.152</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
         <v>0.091</v>
       </c>
-      <c r="Y42" t="n">
-        <v>0.273</v>
-      </c>
       <c r="Z42" t="n">
-        <v>0.394</v>
+        <v>0.364</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
         <v>0.091</v>
       </c>
-      <c r="AI42" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>1.879</v>
-      </c>
       <c r="AM42" t="n">
-        <v>0.339</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>29:00</t>
+          <t>01:19</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>3.821</v>
+        <v>0.455</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.489</v>
+        <v>0.2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.484</v>
+        <v>0.2</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.246</v>
+        <v>0</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.613</v>
+        <v>0</v>
       </c>
       <c r="AV42" t="n">
-        <v>2.968</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.581</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.062</v>
+        <v>0.161</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.01</v>
+        <v>0.165</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="BA42" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#21 O. NETZIPOGLOU (Per Game)</t>
+          <t>#22 T. DORSEY (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="C43" t="n">
-        <v>0.182</v>
+        <v>17</v>
       </c>
       <c r="D43" t="n">
-        <v>0.091</v>
+        <v>2.842</v>
       </c>
       <c r="E43" t="n">
-        <v>0.364</v>
+        <v>5.342</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>2.711</v>
       </c>
       <c r="G43" t="n">
-        <v>0.091</v>
+        <v>6.789</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>3.184</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>3.974</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>2.816</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1.895</v>
       </c>
       <c r="L43" t="n">
-        <v>0.182</v>
+        <v>0.553</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>0.737</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.895</v>
       </c>
       <c r="R43" t="n">
-        <v>0.364</v>
+        <v>1.684</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.842</v>
       </c>
       <c r="T43" t="n">
-        <v>-4</v>
+        <v>619</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.053</v>
       </c>
       <c r="W43" t="n">
-        <v>0.182</v>
+        <v>0.053</v>
       </c>
       <c r="X43" t="n">
-        <v>0.091</v>
+        <v>0.053</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.091</v>
+        <v>3.816</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.364</v>
+        <v>4.263</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.25</v>
+        <v>0.895</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.684</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>3.368</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>0.526</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>0.588</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.553</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.091</v>
+        <v>6.395</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>0.399</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>03:08</t>
+          <t>26:04</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>0.455</v>
+        <v>15.88</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.2</v>
+        <v>0.569</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.2</v>
+        <v>0.612</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.4</v>
+        <v>1.071</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>0.126</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>0.262</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1.408</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>6.066</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>7.474</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.068</v>
+        <v>0.285</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.025</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>0.082</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>0.111</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#22 T. DORSEY (Per Game)</t>
+          <t>#25 A. PETERS (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
         <v>38</v>
       </c>
       <c r="C44" t="n">
-        <v>17</v>
+        <v>6.789</v>
       </c>
       <c r="D44" t="n">
-        <v>2.842</v>
+        <v>1.368</v>
       </c>
       <c r="E44" t="n">
-        <v>5.342</v>
+        <v>2.105</v>
       </c>
       <c r="F44" t="n">
-        <v>2.711</v>
+        <v>0.895</v>
       </c>
       <c r="G44" t="n">
-        <v>6.789</v>
+        <v>2.316</v>
       </c>
       <c r="H44" t="n">
-        <v>3.184</v>
+        <v>1.368</v>
       </c>
       <c r="I44" t="n">
-        <v>3.974</v>
+        <v>1.658</v>
       </c>
       <c r="J44" t="n">
-        <v>2.816</v>
+        <v>0.921</v>
       </c>
       <c r="K44" t="n">
-        <v>1.895</v>
+        <v>1.947</v>
       </c>
       <c r="L44" t="n">
         <v>0.553</v>
       </c>
       <c r="M44" t="n">
-        <v>0.737</v>
+        <v>0.5</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5</v>
+        <v>0.132</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.895</v>
+        <v>0.763</v>
       </c>
       <c r="R44" t="n">
-        <v>1.684</v>
+        <v>1.5</v>
       </c>
       <c r="S44" t="n">
-        <v>3.842</v>
+        <v>1.711</v>
       </c>
       <c r="T44" t="n">
-        <v>619</v>
+        <v>296</v>
       </c>
       <c r="U44" t="n">
-        <v>2.132</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.263</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.316</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.211</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>3.816</v>
+        <v>2.053</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.263</v>
+        <v>2.158</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.895</v>
+        <v>0.951</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.684</v>
+        <v>0.395</v>
       </c>
       <c r="AC44" t="n">
-        <v>3.368</v>
+        <v>0.842</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.5</v>
+        <v>0.469</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.526</v>
+        <v>0.289</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.895</v>
+        <v>0.474</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.588</v>
+        <v>0.611</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.158</v>
+        <v>0.026</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.395</v>
+        <v>0.237</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.4</v>
+        <v>0.111</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.553</v>
+        <v>0.868</v>
       </c>
       <c r="AL44" t="n">
-        <v>6.395</v>
+        <v>2.079</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.399</v>
+        <v>0.418</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>53:27</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>15.88</v>
+        <v>5.966</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.569</v>
+        <v>0.613</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.612</v>
+        <v>0.659</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.071</v>
+        <v>1.138</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.126</v>
+        <v>0.137</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.262</v>
+        <v>0.31</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.408</v>
+        <v>1.129</v>
       </c>
       <c r="AV44" t="n">
-        <v>6.066</v>
+        <v>5.419</v>
       </c>
       <c r="AW44" t="n">
-        <v>7.474</v>
+        <v>6.548</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.139</v>
+        <v>0.19</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.012</v>
+        <v>0.045</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0.04</v>
+        <v>0.149</v>
       </c>
       <c r="BA44" t="n">
-        <v>0.111</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#25 A. PETERS (Per Game)</t>
+          <t>#33 N. MILUTINOV (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C45" t="n">
-        <v>6.789</v>
+        <v>10.571</v>
       </c>
       <c r="D45" t="n">
-        <v>1.368</v>
+        <v>3.6</v>
       </c>
       <c r="E45" t="n">
-        <v>2.105</v>
+        <v>5.2</v>
       </c>
       <c r="F45" t="n">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.316</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>1.368</v>
+        <v>3.371</v>
       </c>
       <c r="I45" t="n">
-        <v>1.658</v>
+        <v>4.257</v>
       </c>
       <c r="J45" t="n">
-        <v>0.921</v>
+        <v>1.371</v>
       </c>
       <c r="K45" t="n">
-        <v>1.947</v>
+        <v>4.029</v>
       </c>
       <c r="L45" t="n">
-        <v>0.553</v>
+        <v>3.114</v>
       </c>
       <c r="M45" t="n">
-        <v>0.5</v>
+        <v>0.657</v>
       </c>
       <c r="N45" t="n">
-        <v>0.132</v>
+        <v>0.857</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.743</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.763</v>
+        <v>0.714</v>
       </c>
       <c r="R45" t="n">
-        <v>1.5</v>
+        <v>0.486</v>
       </c>
       <c r="S45" t="n">
-        <v>1.711</v>
+        <v>3.943</v>
       </c>
       <c r="T45" t="n">
-        <v>296</v>
+        <v>726</v>
       </c>
       <c r="U45" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0.868</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0.368</v>
+        <v>0.114</v>
       </c>
       <c r="X45" t="n">
-        <v>0.184</v>
+        <v>0.057</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.053</v>
+        <v>6.029</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.158</v>
+        <v>6.771</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.951</v>
+        <v>0.89</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.395</v>
+        <v>0.771</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.842</v>
+        <v>1.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.469</v>
+        <v>0.482</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.289</v>
+        <v>0.171</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.474</v>
+        <v>0.2</v>
       </c>
       <c r="AG45" t="n">
-        <v>0.611</v>
+        <v>0.857</v>
       </c>
       <c r="AH45" t="n">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.237</v>
+        <v>0.029</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.868</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.079</v>
+        <v>0.057</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.418</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>25:44</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>5.966</v>
+        <v>7.902</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.613</v>
+        <v>0.681</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.659</v>
+        <v>0.738</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.138</v>
+        <v>1.338</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.137</v>
+        <v>0.094</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.31</v>
+        <v>0.638</v>
       </c>
       <c r="AU45" t="n">
-        <v>1.129</v>
+        <v>1.846</v>
       </c>
       <c r="AV45" t="n">
-        <v>5.419</v>
+        <v>7.115</v>
       </c>
       <c r="AW45" t="n">
-        <v>6.548</v>
+        <v>8.962</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.108</v>
+        <v>0.169</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.026</v>
+        <v>0.171</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.208</v>
       </c>
       <c r="BA45" t="n">
-        <v>0.032</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#33 N. MILUTINOV (Per Game)</t>
+          <t>#34 C. JOSEPH (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="C46" t="n">
-        <v>10.571</v>
+        <v>5.455</v>
       </c>
       <c r="D46" t="n">
-        <v>3.6</v>
+        <v>1.091</v>
       </c>
       <c r="E46" t="n">
-        <v>5.2</v>
+        <v>1.818</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="G46" t="n">
-        <v>0.08599999999999999</v>
+        <v>2.091</v>
       </c>
       <c r="H46" t="n">
-        <v>3.371</v>
+        <v>1.364</v>
       </c>
       <c r="I46" t="n">
-        <v>4.257</v>
+        <v>1.818</v>
       </c>
       <c r="J46" t="n">
-        <v>1.371</v>
+        <v>2.091</v>
       </c>
       <c r="K46" t="n">
-        <v>4.029</v>
+        <v>1.091</v>
       </c>
       <c r="L46" t="n">
-        <v>3.114</v>
+        <v>0.545</v>
       </c>
       <c r="M46" t="n">
-        <v>0.657</v>
+        <v>0.273</v>
       </c>
       <c r="N46" t="n">
-        <v>0.857</v>
+        <v>0.091</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.743</v>
+        <v>1.091</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.714</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0.486</v>
+        <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>3.943</v>
+        <v>2.182</v>
       </c>
       <c r="T46" t="n">
-        <v>726</v>
+        <v>66</v>
       </c>
       <c r="U46" t="n">
-        <v>0.486</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>3.229</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>0.771</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0.571</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>6.029</v>
+        <v>1.818</v>
       </c>
       <c r="Z46" t="n">
-        <v>6.771</v>
+        <v>2.091</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.771</v>
+        <v>0.455</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.6</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.482</v>
+        <v>0.556</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.171</v>
+        <v>0.182</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.2</v>
+        <v>0.273</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.857</v>
+        <v>0.667</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.029</v>
+        <v>0.364</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="AL46" t="n">
-        <v>0.057</v>
+        <v>1.727</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>0.316</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>42:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>7.902</v>
+        <v>5.8</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.681</v>
+        <v>0.523</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.738</v>
+        <v>0.579</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.338</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.094</v>
+        <v>0.188</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.638</v>
+        <v>0.349</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.846</v>
+        <v>1.917</v>
       </c>
       <c r="AV46" t="n">
-        <v>7.115</v>
+        <v>3.583</v>
       </c>
       <c r="AW46" t="n">
-        <v>8.962</v>
+        <v>5.5</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.182</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.044</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.107</v>
+        <v>0.082</v>
       </c>
       <c r="BA46" t="n">
-        <v>0.05</v>
+        <v>0.07199999999999999</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#34 C. JOSEPH (Per Game)</t>
+          <t>#37 K. ANTETOKOUNMPO (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C47" t="n">
-        <v>5.455</v>
+        <v>0.4</v>
       </c>
       <c r="D47" t="n">
-        <v>1.091</v>
+        <v>0.2</v>
       </c>
       <c r="E47" t="n">
-        <v>1.818</v>
+        <v>0.267</v>
       </c>
       <c r="F47" t="n">
-        <v>0.636</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2.091</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.364</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>1.818</v>
+        <v>0.133</v>
       </c>
       <c r="J47" t="n">
-        <v>2.091</v>
+        <v>0.267</v>
       </c>
       <c r="K47" t="n">
-        <v>1.091</v>
+        <v>0.2</v>
       </c>
       <c r="L47" t="n">
-        <v>0.545</v>
+        <v>0.2</v>
       </c>
       <c r="M47" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.091</v>
+        <v>0.067</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0.067</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>0.333</v>
       </c>
       <c r="S47" t="n">
-        <v>2.182</v>
+        <v>0.133</v>
       </c>
       <c r="T47" t="n">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="U47" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.818</v>
+        <v>0.2</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.091</v>
+        <v>0.267</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.455</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.8179999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.556</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.182</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.091</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.364</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.727</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>33:02</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>5.8</v>
+        <v>0.392</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.523</v>
+        <v>0.75</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.579</v>
+        <v>0.615</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.188</v>
+        <v>0.17</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.349</v>
+        <v>0</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.917</v>
+        <v>4</v>
       </c>
       <c r="AV47" t="n">
-        <v>3.583</v>
+        <v>4</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.082</v>
+        <v>0.121</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.02</v>
+        <v>0.159</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.037</v>
+        <v>0.149</v>
       </c>
       <c r="BA47" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#37 K. ANTETOKOUNMPO (Per Game)</t>
+          <t>#45 D. HALL (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4</v>
+        <v>6.486</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2</v>
+        <v>2.514</v>
       </c>
       <c r="E48" t="n">
-        <v>0.267</v>
+        <v>3.243</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1.459</v>
       </c>
       <c r="I48" t="n">
-        <v>0.133</v>
+        <v>1.838</v>
       </c>
       <c r="J48" t="n">
-        <v>0.267</v>
+        <v>0.595</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2</v>
+        <v>2.568</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2</v>
+        <v>1.595</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>0.405</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.067</v>
+        <v>0.486</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.067</v>
+        <v>0.432</v>
       </c>
       <c r="R48" t="n">
-        <v>0.333</v>
+        <v>1.459</v>
       </c>
       <c r="S48" t="n">
-        <v>0.133</v>
+        <v>1.649</v>
       </c>
       <c r="T48" t="n">
-        <v>9</v>
+        <v>411</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="W48" t="n">
-        <v>0.133</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.067</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.2</v>
+        <v>3.622</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.267</v>
+        <v>4.162</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>0.351</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>0.541</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -8031,876 +8031,876 @@
         <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>0.027</v>
       </c>
       <c r="AM48" t="n">
         <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>02:09</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>0.392</v>
+        <v>4.565</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.75</v>
+        <v>0.769</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.615</v>
+        <v>0.795</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.02</v>
+        <v>1.421</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.17</v>
+        <v>0.107</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>0.446</v>
       </c>
       <c r="AU48" t="n">
-        <v>4</v>
+        <v>1.222</v>
       </c>
       <c r="AV48" t="n">
-        <v>4</v>
+        <v>6.722</v>
       </c>
       <c r="AW48" t="n">
-        <v>8</v>
+        <v>7.944</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.154</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.111</v>
+        <v>0.138</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.104</v>
+        <v>0.208</v>
       </c>
       <c r="BA48" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#45 D. HALL (Per Game)</t>
+          <t>#77 S. MCKISSIC (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C49" t="n">
-        <v>6.486</v>
+        <v>3.652</v>
       </c>
       <c r="D49" t="n">
-        <v>2.514</v>
+        <v>0.913</v>
       </c>
       <c r="E49" t="n">
-        <v>3.243</v>
+        <v>1.522</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.261</v>
       </c>
       <c r="G49" t="n">
-        <v>0.027</v>
+        <v>1.304</v>
       </c>
       <c r="H49" t="n">
-        <v>1.459</v>
+        <v>1.043</v>
       </c>
       <c r="I49" t="n">
-        <v>1.838</v>
+        <v>1.696</v>
       </c>
       <c r="J49" t="n">
-        <v>0.595</v>
+        <v>1.435</v>
       </c>
       <c r="K49" t="n">
-        <v>2.568</v>
+        <v>0.826</v>
       </c>
       <c r="L49" t="n">
-        <v>1.595</v>
+        <v>0.261</v>
       </c>
       <c r="M49" t="n">
-        <v>0.405</v>
+        <v>0.783</v>
       </c>
       <c r="N49" t="n">
-        <v>0.892</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.486</v>
+        <v>0.391</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.432</v>
+        <v>0.348</v>
       </c>
       <c r="R49" t="n">
-        <v>1.459</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
-        <v>1.649</v>
+        <v>1.304</v>
       </c>
       <c r="T49" t="n">
-        <v>411</v>
+        <v>107</v>
       </c>
       <c r="U49" t="n">
-        <v>0.486</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.622</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0.757</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0.514</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>3.622</v>
+        <v>1.783</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.162</v>
+        <v>2.087</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.87</v>
+        <v>0.854</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.351</v>
+        <v>0.13</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.541</v>
+        <v>0.348</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.65</v>
+        <v>0.375</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>0.043</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>0.217</v>
       </c>
       <c r="AL49" t="n">
-        <v>0.027</v>
+        <v>1.217</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.179</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>28:21</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>4.565</v>
+        <v>3.963</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.769</v>
+        <v>0.462</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.795</v>
+        <v>0.511</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.421</v>
+        <v>0.921</v>
       </c>
       <c r="AS49" t="n">
-        <v>0.107</v>
+        <v>0.099</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.446</v>
+        <v>0.369</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.222</v>
+        <v>3.667</v>
       </c>
       <c r="AV49" t="n">
-        <v>6.722</v>
+        <v>7.222</v>
       </c>
       <c r="AW49" t="n">
-        <v>7.944</v>
+        <v>10.889</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.075</v>
+        <v>0.168</v>
       </c>
       <c r="AY49" t="n">
-        <v>0.067</v>
+        <v>0.028</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.102</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="BA49" t="n">
-        <v>0.021</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#77 S. MCKISSIC (Per Game)</t>
+          <t>#88 T. JONES (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C50" t="n">
-        <v>3.652</v>
+        <v>7.077</v>
       </c>
       <c r="D50" t="n">
-        <v>0.913</v>
+        <v>2.462</v>
       </c>
       <c r="E50" t="n">
-        <v>1.522</v>
+        <v>3.538</v>
       </c>
       <c r="F50" t="n">
-        <v>0.261</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.304</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1.043</v>
+        <v>2.154</v>
       </c>
       <c r="I50" t="n">
-        <v>1.696</v>
+        <v>3.154</v>
       </c>
       <c r="J50" t="n">
-        <v>1.435</v>
+        <v>1.385</v>
       </c>
       <c r="K50" t="n">
-        <v>0.826</v>
+        <v>2.077</v>
       </c>
       <c r="L50" t="n">
-        <v>0.261</v>
+        <v>1.846</v>
       </c>
       <c r="M50" t="n">
-        <v>0.783</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.391</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.348</v>
+        <v>0.846</v>
       </c>
       <c r="R50" t="n">
-        <v>1</v>
+        <v>1.923</v>
       </c>
       <c r="S50" t="n">
-        <v>1.304</v>
+        <v>2.615</v>
       </c>
       <c r="T50" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="U50" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>0.154</v>
       </c>
       <c r="W50" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.304</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.783</v>
+        <v>4.385</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.087</v>
+        <v>5.231</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.854</v>
+        <v>0.838</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.13</v>
+        <v>0.231</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.348</v>
+        <v>0.462</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.08699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.217</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.217</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.179</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>3.963</v>
+        <v>5.926</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.462</v>
+        <v>0.696</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.511</v>
+        <v>0.718</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.921</v>
+        <v>1.194</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.099</v>
+        <v>0.169</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.369</v>
+        <v>0.609</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.667</v>
+        <v>1.385</v>
       </c>
       <c r="AV50" t="n">
-        <v>7.222</v>
+        <v>3.538</v>
       </c>
       <c r="AW50" t="n">
-        <v>10.889</v>
+        <v>4.923</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.082</v>
+        <v>0.182</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.014</v>
+        <v>0.145</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0.041</v>
+        <v>0.153</v>
       </c>
       <c r="BA50" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>#88 T. JONES (Per Game)</t>
+          <t>#94 E. FOURNIER (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C51" t="n">
-        <v>7.077</v>
+        <v>10.971</v>
       </c>
       <c r="D51" t="n">
-        <v>2.462</v>
+        <v>1.647</v>
       </c>
       <c r="E51" t="n">
-        <v>3.538</v>
+        <v>3.559</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>2.029</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>5.794</v>
       </c>
       <c r="H51" t="n">
-        <v>2.154</v>
+        <v>1.588</v>
       </c>
       <c r="I51" t="n">
-        <v>3.154</v>
+        <v>1.971</v>
       </c>
       <c r="J51" t="n">
-        <v>1.385</v>
+        <v>2.735</v>
       </c>
       <c r="K51" t="n">
-        <v>2.077</v>
+        <v>1.265</v>
       </c>
       <c r="L51" t="n">
-        <v>1.846</v>
+        <v>0.441</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0.765</v>
       </c>
       <c r="N51" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.324</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1</v>
+        <v>1.647</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.846</v>
+        <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>1.923</v>
+        <v>2.029</v>
       </c>
       <c r="S51" t="n">
-        <v>2.615</v>
+        <v>1.618</v>
       </c>
       <c r="T51" t="n">
-        <v>152</v>
+        <v>285</v>
       </c>
       <c r="U51" t="n">
-        <v>0.923</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="V51" t="n">
-        <v>2.077</v>
+        <v>0.059</v>
       </c>
       <c r="W51" t="n">
-        <v>0.462</v>
+        <v>0.059</v>
       </c>
       <c r="X51" t="n">
-        <v>0.385</v>
+        <v>0.029</v>
       </c>
       <c r="Y51" t="n">
-        <v>4.385</v>
+        <v>2.382</v>
       </c>
       <c r="Z51" t="n">
-        <v>5.231</v>
+        <v>3</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.838</v>
+        <v>0.794</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.231</v>
+        <v>0.706</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.462</v>
+        <v>1.735</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.5</v>
+        <v>0.407</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>0.147</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>0.357</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>0.235</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>0.824</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1.794</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>4.971</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>30:11</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>5.926</v>
+        <v>11.867</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.696</v>
+        <v>0.502</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.718</v>
+        <v>0.537</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.194</v>
+        <v>0.924</v>
       </c>
       <c r="AS51" t="n">
-        <v>0.169</v>
+        <v>0.139</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.609</v>
+        <v>0.17</v>
       </c>
       <c r="AU51" t="n">
-        <v>1.385</v>
+        <v>1.661</v>
       </c>
       <c r="AV51" t="n">
-        <v>3.538</v>
+        <v>5.679</v>
       </c>
       <c r="AW51" t="n">
-        <v>4.923</v>
+        <v>7.339</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.092</v>
+        <v>0.258</v>
       </c>
       <c r="AY51" t="n">
-        <v>0.073</v>
+        <v>0.025</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0.077</v>
+        <v>0.066</v>
       </c>
       <c r="BA51" t="n">
-        <v>0.049</v>
+        <v>0.101</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>#94 E. FOURNIER (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>10.971</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1.647</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>3.559</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>2.029</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>5.794</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.588</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>1.971</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>2.735</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>1.265</v>
+        <v>1.921</v>
       </c>
       <c r="L52" t="n">
-        <v>0.441</v>
+        <v>1.921</v>
       </c>
       <c r="M52" t="n">
-        <v>0.765</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>0.324</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.647</v>
+        <v>0.737</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.029</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>1.618</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>285</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.118</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.029</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.059</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0.529</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.382</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.794</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.735</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.407</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0.147</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0.412</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.794</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>4.971</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>0.361</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>42:31</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>11.867</v>
+        <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.502</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.537</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.924</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>1.661</v>
+        <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>5.679</v>
+        <v>0</v>
       </c>
       <c r="AW52" t="n">
-        <v>7.339</v>
+        <v>0</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AY52" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="BA52" t="n">
-        <v>0.101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>38</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>90.26300000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>21.184</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>35.579</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>9.683999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>27.632</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>18.842</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>23.947</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>21.526</v>
       </c>
       <c r="K53" t="n">
-        <v>1.921</v>
+        <v>24.763</v>
       </c>
       <c r="L53" t="n">
-        <v>1.921</v>
+        <v>12.079</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>6.342</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.342</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0.737</v>
+        <v>12.395</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>10.868</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>16.579</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>22.605</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>4389</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>0.632</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>0.368</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>32.289</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>37.763</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>0.855</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>6.289</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>13.921</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>0.452</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.447</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>2.737</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>0.529</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.053</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>3.184</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>0.331</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>8.632</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>24.447</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>0.353</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>86.142</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>0.612</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.048</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>0.298</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>1.737</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>6.837</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>0.138</v>
       </c>
       <c r="BA53" t="n">
         <v>0</v>
@@ -8909,495 +8909,165 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B54" t="n">
         <v>38</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>83.76300000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>20.184</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>36.632</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>10.395</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>28.789</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>12.211</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>15.868</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>19.158</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>21.474</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>7.211</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.342</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>12.421</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>20.579</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>18.342</v>
       </c>
       <c r="T54" t="n">
-        <v>118</v>
+        <v>3564</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>0.263</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>0.289</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>0.395</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>0.158</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>25.053</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>31.237</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>0.802</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>6.211</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>14.474</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.132</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>3.132</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>0.361</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1.632</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>3.737</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>0.437</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>8.763</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>25.053</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>201:18</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>0.737</v>
+        <v>84.824</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>0.547</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>0.578</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>0.987</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>0.187</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>1.542</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>5.267</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>6.809</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>0.197</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>38</v>
-      </c>
-      <c r="C55" t="n">
-        <v>90.26300000000001</v>
-      </c>
-      <c r="D55" t="n">
-        <v>21.184</v>
-      </c>
-      <c r="E55" t="n">
-        <v>35.579</v>
-      </c>
-      <c r="F55" t="n">
-        <v>9.683999999999999</v>
-      </c>
-      <c r="G55" t="n">
-        <v>27.632</v>
-      </c>
-      <c r="H55" t="n">
-        <v>18.842</v>
-      </c>
-      <c r="I55" t="n">
-        <v>23.947</v>
-      </c>
-      <c r="J55" t="n">
-        <v>21.526</v>
-      </c>
-      <c r="K55" t="n">
-        <v>24.763</v>
-      </c>
-      <c r="L55" t="n">
-        <v>12.079</v>
-      </c>
-      <c r="M55" t="n">
-        <v>6.342</v>
-      </c>
-      <c r="N55" t="n">
-        <v>4.342</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>12.395</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>10.868</v>
-      </c>
-      <c r="R55" t="n">
-        <v>16.579</v>
-      </c>
-      <c r="S55" t="n">
-        <v>22.605</v>
-      </c>
-      <c r="T55" t="n">
-        <v>4389</v>
-      </c>
-      <c r="U55" t="n">
-        <v>9.683999999999999</v>
-      </c>
-      <c r="V55" t="n">
-        <v>12.868</v>
-      </c>
-      <c r="W55" t="n">
-        <v>9.132</v>
-      </c>
-      <c r="X55" t="n">
-        <v>5.553</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>32.289</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>37.763</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>6.289</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>13.921</v>
-      </c>
-      <c r="AD55" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="AE55" t="n">
-        <v>1.447</v>
-      </c>
-      <c r="AF55" t="n">
-        <v>2.737</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>3.184</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0.331</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>8.632</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>24.447</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO55" t="n">
-        <v>86.142</v>
-      </c>
-      <c r="AP55" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="AS55" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AT55" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>1.737</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>6.837</v>
-      </c>
-      <c r="AX55" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY55" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="AZ55" t="n">
-        <v>0.138</v>
-      </c>
-      <c r="BA55" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>38</v>
-      </c>
-      <c r="C56" t="n">
-        <v>83.76300000000001</v>
-      </c>
-      <c r="D56" t="n">
-        <v>20.184</v>
-      </c>
-      <c r="E56" t="n">
-        <v>36.632</v>
-      </c>
-      <c r="F56" t="n">
-        <v>10.395</v>
-      </c>
-      <c r="G56" t="n">
-        <v>28.789</v>
-      </c>
-      <c r="H56" t="n">
-        <v>12.211</v>
-      </c>
-      <c r="I56" t="n">
-        <v>15.868</v>
-      </c>
-      <c r="J56" t="n">
-        <v>19.158</v>
-      </c>
-      <c r="K56" t="n">
-        <v>21.474</v>
-      </c>
-      <c r="L56" t="n">
-        <v>11</v>
-      </c>
-      <c r="M56" t="n">
-        <v>7.211</v>
-      </c>
-      <c r="N56" t="n">
-        <v>4.342</v>
-      </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
-        <v>12.421</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>11</v>
-      </c>
-      <c r="R56" t="n">
-        <v>20.579</v>
-      </c>
-      <c r="S56" t="n">
-        <v>18.342</v>
-      </c>
-      <c r="T56" t="n">
-        <v>3564</v>
-      </c>
-      <c r="U56" t="n">
-        <v>9.816000000000001</v>
-      </c>
-      <c r="V56" t="n">
-        <v>11.921</v>
-      </c>
-      <c r="W56" t="n">
-        <v>8.605</v>
-      </c>
-      <c r="X56" t="n">
-        <v>4.632</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>25.053</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>31.237</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>0.802</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>6.211</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>14.474</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>3.132</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1.632</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>3.737</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0.437</v>
-      </c>
-      <c r="AK56" t="n">
-        <v>8.763</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>25.053</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>201:18</t>
-        </is>
-      </c>
-      <c r="AO56" t="n">
-        <v>84.824</v>
-      </c>
-      <c r="AP56" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="AS56" t="n">
-        <v>0.146</v>
-      </c>
-      <c r="AT56" t="n">
-        <v>0.187</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>1.542</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>5.267</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>6.809</v>
-      </c>
-      <c r="AX56" t="n">
-        <v>0.197</v>
-      </c>
-      <c r="AY56" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="AZ56" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA56" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
@@ -671,13 +671,13 @@
         <v>0.2980849292256453</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>503</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="M2" t="n">
         <v>413</v>
@@ -752,13 +752,13 @@
         <v>1.051428571428571</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.02330508474576271</v>
+        <v>0.7923728813559322</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05228758169934641</v>
+        <v>1.095860566448802</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.555555555555556</v>
+        <v>1.637209302325581</v>
       </c>
       <c r="AN2" t="n">
         <v>1.736730360934183</v>
@@ -801,13 +801,13 @@
         <v>0.2980849292256453</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2894736842105263</v>
+        <v>9.842105263157896</v>
       </c>
       <c r="K3" t="n">
-        <v>0.631578947368421</v>
+        <v>13.23684210526316</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3684210526315789</v>
+        <v>9.263157894736842</v>
       </c>
       <c r="M3" t="n">
         <v>10.86842105263158</v>
@@ -882,13 +882,13 @@
         <v>1.051428571428572</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.02330508474576271</v>
+        <v>0.7923728813559323</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0522875816993464</v>
+        <v>1.095860566448802</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.555555555555556</v>
+        <v>1.637209302325581</v>
       </c>
       <c r="AN3" t="n">
         <v>1.736730360934183</v>
@@ -931,13 +931,13 @@
         <v>0.1866452131938858</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>381</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>454</v>
       </c>
       <c r="L4" t="n">
-        <v>15</v>
+        <v>333</v>
       </c>
       <c r="M4" t="n">
         <v>418</v>
@@ -1012,13 +1012,13 @@
         <v>1.083180987202925</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.02123142250530785</v>
+        <v>0.8089171974522293</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02631578947368421</v>
+        <v>1.086124401913876</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.5</v>
+        <v>1.860335195530726</v>
       </c>
       <c r="AN4" t="n">
         <v>1.542372881355932</v>
@@ -1061,13 +1061,13 @@
         <v>0.1866452131938858</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2631578947368421</v>
+        <v>10.02631578947368</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2894736842105263</v>
+        <v>11.94736842105263</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3947368421052632</v>
+        <v>8.763157894736842</v>
       </c>
       <c r="M5" t="n">
         <v>11</v>
@@ -1142,13 +1142,13 @@
         <v>1.083180987202925</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.02123142250530785</v>
+        <v>0.8089171974522293</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.02631578947368421</v>
+        <v>1.086124401913876</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.5</v>
+        <v>1.860335195530726</v>
       </c>
       <c r="AN5" t="n">
         <v>1.542372881355932</v>
@@ -1486,16 +1486,16 @@
         <v>304</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V8" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
         <v>34</v>
@@ -1651,10 +1651,10 @@
         <v>82</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
@@ -1981,16 +1981,16 @@
         <v>281</v>
       </c>
       <c r="U11" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="V11" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y11" t="n">
         <v>102</v>
@@ -2311,16 +2311,16 @@
         <v>25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -2641,16 +2641,16 @@
         <v>14</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
         <v>8</v>
@@ -2806,16 +2806,16 @@
         <v>809</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="Y16" t="n">
         <v>262</v>
@@ -2971,16 +2971,16 @@
         <v>78</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="n">
         <v>9</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
         <v>1</v>
@@ -3301,16 +3301,16 @@
         <v>619</v>
       </c>
       <c r="U19" t="n">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="Y19" t="n">
         <v>145</v>
@@ -3466,16 +3466,16 @@
         <v>296</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Y20" t="n">
         <v>78</v>
@@ -3631,16 +3631,16 @@
         <v>726</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="W21" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
         <v>211</v>
@@ -3796,16 +3796,16 @@
         <v>66</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>20</v>
@@ -3967,10 +3967,10 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
         <v>3</v>
@@ -4126,16 +4126,16 @@
         <v>411</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V24" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y24" t="n">
         <v>134</v>
@@ -4291,16 +4291,16 @@
         <v>107</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y25" t="n">
         <v>41</v>
@@ -4456,16 +4456,16 @@
         <v>152</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V26" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y26" t="n">
         <v>57</v>
@@ -4621,16 +4621,16 @@
         <v>285</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="V27" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Y27" t="n">
         <v>81</v>
@@ -4951,16 +4951,16 @@
         <v>4389</v>
       </c>
       <c r="U29" t="n">
-        <v>11</v>
+        <v>374</v>
       </c>
       <c r="V29" t="n">
-        <v>24</v>
+        <v>503</v>
       </c>
       <c r="W29" t="n">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="X29" t="n">
-        <v>9</v>
+        <v>215</v>
       </c>
       <c r="Y29" t="n">
         <v>1227</v>
@@ -5116,16 +5116,16 @@
         <v>3564</v>
       </c>
       <c r="U30" t="n">
-        <v>10</v>
+        <v>381</v>
       </c>
       <c r="V30" t="n">
-        <v>11</v>
+        <v>454</v>
       </c>
       <c r="W30" t="n">
-        <v>15</v>
+        <v>333</v>
       </c>
       <c r="X30" t="n">
-        <v>6</v>
+        <v>179</v>
       </c>
       <c r="Y30" t="n">
         <v>952</v>
@@ -5340,16 +5340,16 @@
         <v>304</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V32" t="n">
-        <v>0.156</v>
+        <v>0.438</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="Y32" t="n">
         <v>1.062</v>
@@ -5505,10 +5505,10 @@
         <v>82</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.609</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5835,16 +5835,16 @@
         <v>281</v>
       </c>
       <c r="U35" t="n">
-        <v>0.062</v>
+        <v>1.281</v>
       </c>
       <c r="V35" t="n">
-        <v>0.062</v>
+        <v>0.875</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>0.906</v>
       </c>
       <c r="Y35" t="n">
         <v>3.188</v>
@@ -6165,16 +6165,16 @@
         <v>25</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.176</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="Y37" t="n">
         <v>0.824</v>
@@ -6495,16 +6495,16 @@
         <v>14</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y39" t="n">
         <v>0.8</v>
@@ -6660,16 +6660,16 @@
         <v>809</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.412</v>
       </c>
       <c r="V40" t="n">
-        <v>0.176</v>
+        <v>2.941</v>
       </c>
       <c r="W40" t="n">
-        <v>0.147</v>
+        <v>2.324</v>
       </c>
       <c r="X40" t="n">
-        <v>0.08799999999999999</v>
+        <v>1.471</v>
       </c>
       <c r="Y40" t="n">
         <v>7.706</v>
@@ -6825,16 +6825,16 @@
         <v>78</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.212</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="W41" t="n">
-        <v>0.03</v>
+        <v>0.152</v>
       </c>
       <c r="X41" t="n">
-        <v>0.03</v>
+        <v>0.091</v>
       </c>
       <c r="Y41" t="n">
         <v>0.273</v>
@@ -6996,10 +6996,10 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="Y42" t="n">
         <v>0.091</v>
@@ -7155,16 +7155,16 @@
         <v>619</v>
       </c>
       <c r="U43" t="n">
-        <v>0.158</v>
+        <v>2.237</v>
       </c>
       <c r="V43" t="n">
-        <v>0.053</v>
+        <v>1.421</v>
       </c>
       <c r="W43" t="n">
-        <v>0.053</v>
+        <v>2.316</v>
       </c>
       <c r="X43" t="n">
-        <v>0.053</v>
+        <v>1.211</v>
       </c>
       <c r="Y43" t="n">
         <v>3.816</v>
@@ -7320,16 +7320,16 @@
         <v>296</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.921</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>0.421</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="Y44" t="n">
         <v>2.053</v>
@@ -7485,16 +7485,16 @@
         <v>726</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>0.486</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>3.114</v>
       </c>
       <c r="W45" t="n">
-        <v>0.114</v>
+        <v>0.8</v>
       </c>
       <c r="X45" t="n">
-        <v>0.057</v>
+        <v>0.6</v>
       </c>
       <c r="Y45" t="n">
         <v>6.029</v>
@@ -7650,16 +7650,16 @@
         <v>66</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.091</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>0.091</v>
       </c>
       <c r="Y46" t="n">
         <v>1.818</v>
@@ -7821,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="Y47" t="n">
         <v>0.2</v>
@@ -7980,16 +7980,16 @@
         <v>411</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="V48" t="n">
-        <v>0.135</v>
+        <v>1.649</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>0.757</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>0.514</v>
       </c>
       <c r="Y48" t="n">
         <v>3.622</v>
@@ -8145,16 +8145,16 @@
         <v>107</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.391</v>
       </c>
       <c r="Y49" t="n">
         <v>1.783</v>
@@ -8310,16 +8310,16 @@
         <v>152</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>0.923</v>
       </c>
       <c r="V50" t="n">
-        <v>0.154</v>
+        <v>2.077</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>0.308</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>0.231</v>
       </c>
       <c r="Y50" t="n">
         <v>4.385</v>
@@ -8475,16 +8475,16 @@
         <v>285</v>
       </c>
       <c r="U51" t="n">
-        <v>0.08799999999999999</v>
+        <v>1.118</v>
       </c>
       <c r="V51" t="n">
-        <v>0.059</v>
+        <v>1.176</v>
       </c>
       <c r="W51" t="n">
-        <v>0.059</v>
+        <v>1.059</v>
       </c>
       <c r="X51" t="n">
-        <v>0.029</v>
+        <v>0.529</v>
       </c>
       <c r="Y51" t="n">
         <v>2.382</v>
@@ -8805,16 +8805,16 @@
         <v>4389</v>
       </c>
       <c r="U53" t="n">
-        <v>0.289</v>
+        <v>9.842000000000001</v>
       </c>
       <c r="V53" t="n">
-        <v>0.632</v>
+        <v>13.237</v>
       </c>
       <c r="W53" t="n">
-        <v>0.368</v>
+        <v>9.263</v>
       </c>
       <c r="X53" t="n">
-        <v>0.237</v>
+        <v>5.658</v>
       </c>
       <c r="Y53" t="n">
         <v>32.289</v>
@@ -8970,16 +8970,16 @@
         <v>3564</v>
       </c>
       <c r="U54" t="n">
-        <v>0.263</v>
+        <v>10.026</v>
       </c>
       <c r="V54" t="n">
-        <v>0.289</v>
+        <v>11.947</v>
       </c>
       <c r="W54" t="n">
-        <v>0.395</v>
+        <v>8.763</v>
       </c>
       <c r="X54" t="n">
-        <v>0.158</v>
+        <v>4.711</v>
       </c>
       <c r="Y54" t="n">
         <v>25.053</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
@@ -683,13 +683,13 @@
         <v>413</v>
       </c>
       <c r="N2" t="n">
-        <v>1227</v>
+        <v>511</v>
       </c>
       <c r="O2" t="n">
-        <v>1435</v>
+        <v>719</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5974188176519567</v>
+        <v>0.2993338884263114</v>
       </c>
       <c r="Q2" t="n">
         <v>239</v>
@@ -710,25 +710,25 @@
         <v>0.04329725228975854</v>
       </c>
       <c r="W2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="X2" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.05037468776019983</v>
+        <v>0.05953372189841798</v>
       </c>
       <c r="Z2" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="AA2" t="n">
-        <v>929</v>
+        <v>907</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3867610324729392</v>
+        <v>0.3776019983347211</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8550522648083624</v>
+        <v>0.7107093184979137</v>
       </c>
       <c r="AD2" t="n">
         <v>0.4517958412098299</v>
@@ -737,13 +737,13 @@
         <v>0.5288461538461539</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3305785123966942</v>
+        <v>0.3286713286713286</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3530678148546825</v>
+        <v>0.3539140022050717</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.710104529616725</v>
+        <v>1.421418636995827</v>
       </c>
       <c r="AI2" t="n">
         <v>1.057692307692308</v>
@@ -813,13 +813,13 @@
         <v>10.86842105263158</v>
       </c>
       <c r="N3" t="n">
-        <v>32.28947368421053</v>
+        <v>13.44736842105263</v>
       </c>
       <c r="O3" t="n">
-        <v>37.76315789473684</v>
+        <v>18.92105263157895</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5974188176519567</v>
+        <v>0.2993338884263114</v>
       </c>
       <c r="Q3" t="n">
         <v>6.289473684210527</v>
@@ -840,25 +840,25 @@
         <v>0.04329725228975853</v>
       </c>
       <c r="W3" t="n">
-        <v>1.052631578947368</v>
+        <v>1.236842105263158</v>
       </c>
       <c r="X3" t="n">
-        <v>3.184210526315789</v>
+        <v>3.763157894736842</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.05037468776019983</v>
+        <v>0.05953372189841798</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.631578947368421</v>
+        <v>8.447368421052632</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.44736842105263</v>
+        <v>23.86842105263158</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3867610324729391</v>
+        <v>0.377601998334721</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8550522648083624</v>
+        <v>0.7107093184979137</v>
       </c>
       <c r="AD3" t="n">
         <v>0.4517958412098299</v>
@@ -867,19 +867,19 @@
         <v>0.5288461538461539</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3305785123966942</v>
+        <v>0.3286713286713287</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3530678148546825</v>
+        <v>0.3539140022050717</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.710104529616725</v>
+        <v>1.421418636995827</v>
       </c>
       <c r="AI3" t="n">
         <v>1.057692307692308</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.051428571428572</v>
+        <v>1.051428571428571</v>
       </c>
       <c r="AK3" t="n">
         <v>0.7923728813559323</v>
@@ -943,13 +943,13 @@
         <v>418</v>
       </c>
       <c r="N4" t="n">
-        <v>952</v>
+        <v>488</v>
       </c>
       <c r="O4" t="n">
-        <v>1187</v>
+        <v>723</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4774738535800483</v>
+        <v>0.2908286403861625</v>
       </c>
       <c r="Q4" t="n">
         <v>236</v>
@@ -970,25 +970,25 @@
         <v>0.04786806114239742</v>
       </c>
       <c r="W4" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="X4" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.05711987127916331</v>
+        <v>0.06637168141592921</v>
       </c>
       <c r="Z4" t="n">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AA4" t="n">
-        <v>952</v>
+        <v>929</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3829444891391794</v>
+        <v>0.3736926790024135</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.802021903959562</v>
+        <v>0.6749654218533887</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4290909090909091</v>
@@ -997,13 +997,13 @@
         <v>0.361344537815126</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4366197183098591</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3497899159663865</v>
+        <v>0.3509149623250807</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.604043807919124</v>
+        <v>1.349930843706777</v>
       </c>
       <c r="AI4" t="n">
         <v>0.7226890756302521</v>
@@ -1073,13 +1073,13 @@
         <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>25.05263157894737</v>
+        <v>12.8421052631579</v>
       </c>
       <c r="O5" t="n">
-        <v>31.23684210526316</v>
+        <v>19.02631578947368</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4774738535800483</v>
+        <v>0.2908286403861625</v>
       </c>
       <c r="Q5" t="n">
         <v>6.210526315789473</v>
@@ -1100,25 +1100,25 @@
         <v>0.04786806114239743</v>
       </c>
       <c r="W5" t="n">
-        <v>1.631578947368421</v>
+        <v>1.815789473684211</v>
       </c>
       <c r="X5" t="n">
-        <v>3.736842105263158</v>
+        <v>4.342105263157895</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.05711987127916332</v>
+        <v>0.06637168141592921</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.763157894736842</v>
+        <v>8.578947368421053</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.05263157894737</v>
+        <v>24.44736842105263</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3829444891391794</v>
+        <v>0.3736926790024135</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.802021903959562</v>
+        <v>0.6749654218533887</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4290909090909091</v>
@@ -1127,13 +1127,13 @@
         <v>0.361344537815126</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4366197183098591</v>
+        <v>0.4181818181818182</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3497899159663865</v>
+        <v>0.3509149623250808</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.604043807919124</v>
+        <v>1.349930843706777</v>
       </c>
       <c r="AI5" t="n">
         <v>0.7226890756302521</v>
@@ -1498,13 +1498,13 @@
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="Z8" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.756</v>
+        <v>0.633</v>
       </c>
       <c r="AB8" t="n">
         <v>12</v>
@@ -1528,19 +1528,19 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AK8" t="n">
         <v>23</v>
       </c>
       <c r="AL8" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.315</v>
+        <v>0.319</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1663,13 +1663,13 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.765</v>
+        <v>0.556</v>
       </c>
       <c r="AB9" t="n">
         <v>5</v>
@@ -1690,22 +1690,22 @@
         <v>0.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.383</v>
+        <v>0.364</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         <v>29</v>
       </c>
       <c r="Y11" t="n">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="Z11" t="n">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.779</v>
+        <v>0.628</v>
       </c>
       <c r="AB11" t="n">
         <v>13</v>
@@ -2023,19 +2023,19 @@
         <v>5</v>
       </c>
       <c r="AI11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.417</v>
+        <v>0.357</v>
       </c>
       <c r="AK11" t="n">
         <v>12</v>
       </c>
       <c r="AL11" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.214</v>
+        <v>0.222</v>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
@@ -2323,13 +2323,13 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z13" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.875</v>
+        <v>0.714</v>
       </c>
       <c r="AB13" t="n">
         <v>3</v>
@@ -2350,22 +2350,22 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.364</v>
+        <v>0.3</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
@@ -2653,13 +2653,13 @@
         <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>50</v>
       </c>
       <c r="Y16" t="n">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="Z16" t="n">
-        <v>301</v>
+        <v>153</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.87</v>
+        <v>0.745</v>
       </c>
       <c r="AB16" t="n">
         <v>51</v>
@@ -2845,22 +2845,22 @@
         <v>0.333</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="AK16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AL16" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.378</v>
+        <v>0.382</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
@@ -2983,13 +2983,13 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="AB17" t="n">
         <v>1</v>
@@ -3010,22 +3010,22 @@
         <v>1</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.188</v>
+        <v>0.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
@@ -3313,13 +3313,13 @@
         <v>46</v>
       </c>
       <c r="Y19" t="n">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="Z19" t="n">
-        <v>162</v>
+        <v>41</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.895</v>
+        <v>0.585</v>
       </c>
       <c r="AB19" t="n">
         <v>64</v>
@@ -3340,22 +3340,22 @@
         <v>0.588</v>
       </c>
       <c r="AH19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.4</v>
+        <v>0.438</v>
       </c>
       <c r="AK19" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AL19" t="n">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.399</v>
+        <v>0.397</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
@@ -3478,13 +3478,13 @@
         <v>8</v>
       </c>
       <c r="Y20" t="n">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="Z20" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.951</v>
+        <v>0.867</v>
       </c>
       <c r="AB20" t="n">
         <v>15</v>
@@ -3505,22 +3505,22 @@
         <v>0.611</v>
       </c>
       <c r="AH20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.111</v>
+        <v>0.154</v>
       </c>
       <c r="AK20" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AL20" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
-        <v>0.418</v>
+        <v>0.427</v>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
@@ -3643,13 +3643,13 @@
         <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>211</v>
+        <v>93</v>
       </c>
       <c r="Z21" t="n">
-        <v>237</v>
+        <v>119</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.89</v>
+        <v>0.782</v>
       </c>
       <c r="AB21" t="n">
         <v>27</v>
@@ -3808,13 +3808,13 @@
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.87</v>
+        <v>0.625</v>
       </c>
       <c r="AB22" t="n">
         <v>5</v>
@@ -4138,13 +4138,13 @@
         <v>19</v>
       </c>
       <c r="Y24" t="n">
-        <v>134</v>
+        <v>80</v>
       </c>
       <c r="Z24" t="n">
-        <v>154</v>
+        <v>100</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="AB24" t="n">
         <v>13</v>
@@ -4303,13 +4303,13 @@
         <v>9</v>
       </c>
       <c r="Y25" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="Z25" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.854</v>
+        <v>0.708</v>
       </c>
       <c r="AB25" t="n">
         <v>3</v>
@@ -4333,19 +4333,19 @@
         <v>1</v>
       </c>
       <c r="AI25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK25" t="n">
         <v>5</v>
       </c>
       <c r="AL25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.179</v>
+        <v>0.185</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
@@ -4468,13 +4468,13 @@
         <v>3</v>
       </c>
       <c r="Y26" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="Z26" t="n">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.838</v>
+        <v>0.725</v>
       </c>
       <c r="AB26" t="n">
         <v>3</v>
@@ -4633,13 +4633,13 @@
         <v>18</v>
       </c>
       <c r="Y27" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="Z27" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.794</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AB27" t="n">
         <v>24</v>
@@ -4963,13 +4963,13 @@
         <v>215</v>
       </c>
       <c r="Y29" t="n">
-        <v>1227</v>
+        <v>511</v>
       </c>
       <c r="Z29" t="n">
-        <v>1435</v>
+        <v>719</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.855</v>
+        <v>0.711</v>
       </c>
       <c r="AB29" t="n">
         <v>239</v>
@@ -4990,22 +4990,22 @@
         <v>0.529</v>
       </c>
       <c r="AH29" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="AI29" t="n">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="AK29" t="n">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="AL29" t="n">
-        <v>929</v>
+        <v>907</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
@@ -5128,13 +5128,13 @@
         <v>179</v>
       </c>
       <c r="Y30" t="n">
-        <v>952</v>
+        <v>488</v>
       </c>
       <c r="Z30" t="n">
-        <v>1187</v>
+        <v>723</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.802</v>
+        <v>0.675</v>
       </c>
       <c r="AB30" t="n">
         <v>236</v>
@@ -5155,22 +5155,22 @@
         <v>0.361</v>
       </c>
       <c r="AH30" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="AI30" t="n">
-        <v>142</v>
+        <v>165</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.437</v>
+        <v>0.418</v>
       </c>
       <c r="AK30" t="n">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="AL30" t="n">
-        <v>952</v>
+        <v>929</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>0.094</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.062</v>
+        <v>0.594</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.406</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.756</v>
+        <v>0.633</v>
       </c>
       <c r="AB32" t="n">
         <v>0.375</v>
@@ -5382,19 +5382,19 @@
         <v>0.094</v>
       </c>
       <c r="AI32" t="n">
-        <v>0.281</v>
+        <v>0.312</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.333</v>
+        <v>0.3</v>
       </c>
       <c r="AK32" t="n">
         <v>0.719</v>
       </c>
       <c r="AL32" t="n">
-        <v>2.281</v>
+        <v>2.25</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.315</v>
+        <v>0.319</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.13</v>
+        <v>0.435</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.478</v>
+        <v>0.783</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.765</v>
+        <v>0.556</v>
       </c>
       <c r="AB33" t="n">
         <v>0.217</v>
@@ -5544,22 +5544,22 @@
         <v>0.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0.043</v>
+        <v>0.13</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.217</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AK33" t="n">
-        <v>0.783</v>
+        <v>0.696</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.043</v>
+        <v>1.913</v>
       </c>
       <c r="AM33" t="n">
-        <v>0.383</v>
+        <v>0.364</v>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
@@ -5847,13 +5847,13 @@
         <v>0.906</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.188</v>
+        <v>1.531</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.094</v>
+        <v>2.438</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.779</v>
+        <v>0.628</v>
       </c>
       <c r="AB35" t="n">
         <v>0.406</v>
@@ -5877,19 +5877,19 @@
         <v>0.156</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.375</v>
+        <v>0.438</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.417</v>
+        <v>0.357</v>
       </c>
       <c r="AK35" t="n">
         <v>0.375</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.75</v>
+        <v>1.688</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.214</v>
+        <v>0.222</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
@@ -6177,13 +6177,13 @@
         <v>0.059</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.824</v>
+        <v>0.294</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.412</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.875</v>
+        <v>0.714</v>
       </c>
       <c r="AB37" t="n">
         <v>0.176</v>
@@ -6204,22 +6204,22 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>0.059</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.235</v>
+        <v>0.176</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.647</v>
+        <v>0.588</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.364</v>
+        <v>0.3</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6507,13 +6507,13 @@
         <v>0.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.8</v>
+        <v>0.333</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="AJ39" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AM39" t="n">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>1.471</v>
       </c>
       <c r="Y40" t="n">
-        <v>7.706</v>
+        <v>3.353</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.853</v>
+        <v>4.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.87</v>
+        <v>0.745</v>
       </c>
       <c r="AB40" t="n">
         <v>1.5</v>
@@ -6699,22 +6699,22 @@
         <v>0.333</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.324</v>
+        <v>0.353</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.647</v>
+        <v>0.765</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.412</v>
+        <v>1.382</v>
       </c>
       <c r="AL40" t="n">
-        <v>3.735</v>
+        <v>3.618</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.378</v>
+        <v>0.382</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>0.091</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.273</v>
+        <v>0.212</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.394</v>
+        <v>0.333</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.636</v>
       </c>
       <c r="AB41" t="n">
         <v>0.03</v>
@@ -6864,22 +6864,22 @@
         <v>1</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.091</v>
+        <v>0.121</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.485</v>
+        <v>0.606</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.188</v>
+        <v>0.2</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.636</v>
+        <v>0.606</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.879</v>
+        <v>1.758</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.339</v>
+        <v>0.345</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -7167,13 +7167,13 @@
         <v>1.211</v>
       </c>
       <c r="Y43" t="n">
-        <v>3.816</v>
+        <v>0.632</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.263</v>
+        <v>1.079</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.895</v>
+        <v>0.585</v>
       </c>
       <c r="AB43" t="n">
         <v>1.684</v>
@@ -7194,22 +7194,22 @@
         <v>0.588</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.158</v>
+        <v>0.184</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.395</v>
+        <v>0.421</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.4</v>
+        <v>0.438</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.553</v>
+        <v>2.526</v>
       </c>
       <c r="AL43" t="n">
-        <v>6.395</v>
+        <v>6.368</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.399</v>
+        <v>0.397</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
@@ -7332,13 +7332,13 @@
         <v>0.211</v>
       </c>
       <c r="Y44" t="n">
-        <v>2.053</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.158</v>
+        <v>0.789</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.951</v>
+        <v>0.867</v>
       </c>
       <c r="AB44" t="n">
         <v>0.395</v>
@@ -7359,22 +7359,22 @@
         <v>0.611</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.026</v>
+        <v>0.053</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.237</v>
+        <v>0.342</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.111</v>
+        <v>0.154</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.868</v>
+        <v>0.842</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.079</v>
+        <v>1.974</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.418</v>
+        <v>0.427</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
@@ -7497,13 +7497,13 @@
         <v>0.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>6.029</v>
+        <v>2.657</v>
       </c>
       <c r="Z45" t="n">
-        <v>6.771</v>
+        <v>3.4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.89</v>
+        <v>0.782</v>
       </c>
       <c r="AB45" t="n">
         <v>0.771</v>
@@ -7662,13 +7662,13 @@
         <v>0.091</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.818</v>
+        <v>0.455</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.091</v>
+        <v>0.727</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.87</v>
+        <v>0.625</v>
       </c>
       <c r="AB46" t="n">
         <v>0.455</v>
@@ -7992,13 +7992,13 @@
         <v>0.514</v>
       </c>
       <c r="Y48" t="n">
-        <v>3.622</v>
+        <v>2.162</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.162</v>
+        <v>2.703</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.87</v>
+        <v>0.8</v>
       </c>
       <c r="AB48" t="n">
         <v>0.351</v>
@@ -8157,13 +8157,13 @@
         <v>0.391</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.783</v>
+        <v>0.739</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.087</v>
+        <v>1.043</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.854</v>
+        <v>0.708</v>
       </c>
       <c r="AB49" t="n">
         <v>0.13</v>
@@ -8187,19 +8187,19 @@
         <v>0.043</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AK49" t="n">
         <v>0.217</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.217</v>
+        <v>1.174</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.179</v>
+        <v>0.185</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
@@ -8322,13 +8322,13 @@
         <v>0.231</v>
       </c>
       <c r="Y50" t="n">
-        <v>4.385</v>
+        <v>2.231</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.231</v>
+        <v>3.077</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.838</v>
+        <v>0.725</v>
       </c>
       <c r="AB50" t="n">
         <v>0.231</v>
@@ -8487,13 +8487,13 @@
         <v>0.529</v>
       </c>
       <c r="Y51" t="n">
-        <v>2.382</v>
+        <v>0.794</v>
       </c>
       <c r="Z51" t="n">
-        <v>3</v>
+        <v>1.412</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.794</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AB51" t="n">
         <v>0.706</v>
@@ -8817,13 +8817,13 @@
         <v>5.658</v>
       </c>
       <c r="Y53" t="n">
-        <v>32.289</v>
+        <v>13.447</v>
       </c>
       <c r="Z53" t="n">
-        <v>37.763</v>
+        <v>18.921</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.855</v>
+        <v>0.711</v>
       </c>
       <c r="AB53" t="n">
         <v>6.289</v>
@@ -8844,22 +8844,22 @@
         <v>0.529</v>
       </c>
       <c r="AH53" t="n">
-        <v>1.053</v>
+        <v>1.237</v>
       </c>
       <c r="AI53" t="n">
-        <v>3.184</v>
+        <v>3.763</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="AK53" t="n">
-        <v>8.632</v>
+        <v>8.446999999999999</v>
       </c>
       <c r="AL53" t="n">
-        <v>24.447</v>
+        <v>23.868</v>
       </c>
       <c r="AM53" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
@@ -8982,13 +8982,13 @@
         <v>4.711</v>
       </c>
       <c r="Y54" t="n">
-        <v>25.053</v>
+        <v>12.842</v>
       </c>
       <c r="Z54" t="n">
-        <v>31.237</v>
+        <v>19.026</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.802</v>
+        <v>0.675</v>
       </c>
       <c r="AB54" t="n">
         <v>6.211</v>
@@ -9009,22 +9009,22 @@
         <v>0.361</v>
       </c>
       <c r="AH54" t="n">
-        <v>1.632</v>
+        <v>1.816</v>
       </c>
       <c r="AI54" t="n">
-        <v>3.737</v>
+        <v>4.342</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.437</v>
+        <v>0.418</v>
       </c>
       <c r="AK54" t="n">
-        <v>8.763</v>
+        <v>8.579000000000001</v>
       </c>
       <c r="AL54" t="n">
-        <v>25.053</v>
+        <v>24.447</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
